--- a/mba_sem/static/tr/MBA_FINANCE_TR_4_SEM.xlsx
+++ b/mba_sem/static/tr/MBA_FINANCE_TR_4_SEM.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="66">
   <si>
     <t xml:space="preserve">                                                         Purnea University, Purnia, Bihar</t>
   </si>
@@ -139,9 +139,6 @@
   </si>
   <si>
     <t xml:space="preserve">Credit Earned</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GP</t>
   </si>
   <si>
     <t xml:space="preserve">GP = C.E X N.G</t>
@@ -557,9 +554,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>24</xdr:col>
-      <xdr:colOff>52920</xdr:colOff>
+      <xdr:colOff>52560</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>1252080</xdr:rowOff>
+      <xdr:rowOff>1251720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -572,8 +569,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8500680" y="290880"/>
-          <a:ext cx="959040" cy="961200"/>
+          <a:off x="8499600" y="290880"/>
+          <a:ext cx="957240" cy="960840"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -597,7 +594,7 @@
   <sheetFormatPr defaultColWidth="9.1015625" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="9.09"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="11.37"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="11.38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="12.1"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="6.54"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="5.72"/>
@@ -1155,7 +1152,7 @@
         <v>37</v>
       </c>
       <c r="Z7" s="19" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AA7" s="19" t="s">
         <v>32</v>
@@ -1173,7 +1170,7 @@
         <v>37</v>
       </c>
       <c r="AF7" s="19" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AG7" s="19" t="s">
         <v>32</v>
@@ -1194,7 +1191,7 @@
         <v>37</v>
       </c>
       <c r="AM7" s="19" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AN7" s="20"/>
       <c r="AO7" s="19" t="s">
@@ -1216,7 +1213,7 @@
         <v>37</v>
       </c>
       <c r="AU7" s="19" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AV7" s="19" t="s">
         <v>32</v>
@@ -1237,10 +1234,10 @@
         <v>37</v>
       </c>
       <c r="BB7" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="BC7" s="21" t="s">
         <v>39</v>
-      </c>
-      <c r="BC7" s="21" t="s">
-        <v>40</v>
       </c>
       <c r="BD7" s="21"/>
       <c r="BE7" s="15" t="n">
@@ -1248,11 +1245,11 @@
       </c>
       <c r="BF7" s="15"/>
       <c r="BG7" s="18" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="BH7" s="18"/>
       <c r="BI7" s="18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="BJ7" s="18"/>
       <c r="BK7" s="13"/>
@@ -1313,7 +1310,7 @@
       <c r="BA8" s="19"/>
       <c r="BB8" s="19"/>
       <c r="BC8" s="21" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="BD8" s="21"/>
       <c r="BE8" s="15" t="n">
@@ -1321,11 +1318,11 @@
       </c>
       <c r="BF8" s="15"/>
       <c r="BG8" s="18" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="BH8" s="18"/>
       <c r="BI8" s="18" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="BJ8" s="18"/>
       <c r="BK8" s="13"/>
@@ -1386,7 +1383,7 @@
       <c r="BA9" s="19"/>
       <c r="BB9" s="19"/>
       <c r="BC9" s="21" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="BD9" s="21"/>
       <c r="BE9" s="15" t="n">
@@ -1394,11 +1391,11 @@
       </c>
       <c r="BF9" s="15"/>
       <c r="BG9" s="18" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="BH9" s="18"/>
       <c r="BI9" s="18" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="BJ9" s="18"/>
       <c r="BK9" s="13"/>
@@ -1459,7 +1456,7 @@
       <c r="BA10" s="19"/>
       <c r="BB10" s="19"/>
       <c r="BC10" s="21" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="BD10" s="21"/>
       <c r="BE10" s="15" t="n">
@@ -1467,11 +1464,11 @@
       </c>
       <c r="BF10" s="15"/>
       <c r="BG10" s="18" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="BH10" s="18"/>
       <c r="BI10" s="18" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="BJ10" s="18"/>
       <c r="BK10" s="13"/>
@@ -1532,7 +1529,7 @@
       <c r="BA11" s="19"/>
       <c r="BB11" s="19"/>
       <c r="BC11" s="21" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="BD11" s="21"/>
       <c r="BE11" s="15" t="n">
@@ -1540,11 +1537,11 @@
       </c>
       <c r="BF11" s="15"/>
       <c r="BG11" s="18" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="BH11" s="18"/>
       <c r="BI11" s="18" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="BJ11" s="18"/>
       <c r="BK11" s="13"/>
@@ -1605,19 +1602,19 @@
       <c r="BA12" s="19"/>
       <c r="BB12" s="19"/>
       <c r="BC12" s="22" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="BD12" s="22"/>
       <c r="BE12" s="15" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="BF12" s="15"/>
       <c r="BG12" s="18" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="BH12" s="18"/>
       <c r="BI12" s="18" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="BJ12" s="18"/>
       <c r="BK12" s="13"/>
@@ -1678,7 +1675,7 @@
       <c r="BA13" s="19"/>
       <c r="BB13" s="19"/>
       <c r="BC13" s="22" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="BD13" s="22"/>
       <c r="BE13" s="22"/>
@@ -1693,7 +1690,7 @@
       <c r="A14" s="13"/>
       <c r="B14" s="13"/>
       <c r="C14" s="17" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D14" s="17"/>
       <c r="E14" s="17"/>
@@ -1793,19 +1790,19 @@
       <c r="BA14" s="17"/>
       <c r="BB14" s="17"/>
       <c r="BC14" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="BD14" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="BD14" s="13" t="s">
+      <c r="BE14" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="BE14" s="13" t="s">
+      <c r="BF14" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="BF14" s="13" t="s">
+      <c r="BG14" s="13" t="s">
         <v>64</v>
-      </c>
-      <c r="BG14" s="13" t="s">
-        <v>65</v>
       </c>
       <c r="BH14" s="13" t="s">
         <v>16</v>
@@ -1822,7 +1819,7 @@
       <c r="A15" s="13"/>
       <c r="B15" s="13"/>
       <c r="C15" s="17" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D15" s="17"/>
       <c r="E15" s="17"/>
